--- a/协作/模板/37-发布历史.xlsx
+++ b/协作/模板/37-发布历史.xlsx
@@ -1722,8 +1722,8 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
-      <formula1>"已发布,已回滚,已废弃"</formula1>
+    <dataValidation sqref="G2:G121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"未发布,已发布,已回滚,已废弃"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
